--- a/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD_PYRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD_PYRAD/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.68 ± 0.09</t>
+          <t>0.67 ± 0.09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.42 ± 0.09</t>
+          <t>0.40 ± 0.08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.50 ± 0.31</t>
+          <t>0.48 ± 0.33</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.62 ± 0.40</t>
+          <t>0.60 ± 0.39</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.57 ± 0.30</t>
+          <t>0.59 ± 0.29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,17 +528,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.73 ± 0.27</t>
+          <t>0.69 ± 0.25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
